--- a/construction_cost_predictor/outputs/05_shap_importance.xlsx
+++ b/construction_cost_predictor/outputs/05_shap_importance.xlsx
@@ -440,7 +440,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.09194651246070862</v>
+        <v>0.1271530985832214</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.06071849912405014</v>
+        <v>0.05571621283888817</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
@@ -462,11 +462,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>province_贵州</t>
+          <t>above_floors</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02856405265629292</v>
+        <v>0.02567492984235287</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
@@ -475,11 +475,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>province_浙江</t>
+          <t>province_北京</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0268048457801342</v>
+        <v>0.02556025795638561</v>
       </c>
       <c r="C5" t="n">
         <v>4</v>
@@ -488,11 +488,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cement_price_index</t>
+          <t>province_广东</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02575273625552654</v>
+        <v>0.02313975244760513</v>
       </c>
       <c r="C6" t="n">
         <v>5</v>
@@ -501,11 +501,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>province_广东</t>
+          <t>province_贵州</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02047642506659031</v>
+        <v>0.02173587121069431</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
@@ -514,11 +514,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>province_河北</t>
+          <t>province_河南</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01797866262495518</v>
+        <v>0.0209201592952013</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
@@ -527,11 +527,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>province_安徽</t>
+          <t>province_湖南</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01609148643910885</v>
+        <v>0.01822876743972301</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
@@ -540,11 +540,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>province_云南</t>
+          <t>province_浙江</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01599198020994663</v>
+        <v>0.01773909479379654</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
@@ -553,11 +553,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>above_floors</t>
+          <t>floor_density</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0148545503616333</v>
+        <v>0.01460226625204086</v>
       </c>
       <c r="C11" t="n">
         <v>10</v>
@@ -566,11 +566,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>province_北京</t>
+          <t>province_河北</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.01380199007689953</v>
+        <v>0.01279153395444155</v>
       </c>
       <c r="C12" t="n">
         <v>11</v>
@@ -579,11 +579,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>floor_density</t>
+          <t>province_陕西</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.01236523035913706</v>
+        <v>0.01255027949810028</v>
       </c>
       <c r="C13" t="n">
         <v>12</v>
@@ -592,11 +592,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>province_河南</t>
+          <t>province_云南</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.009293531067669392</v>
+        <v>0.01246369164437056</v>
       </c>
       <c r="C14" t="n">
         <v>13</v>
@@ -605,11 +605,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>total_area</t>
+          <t>province_安徽</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.00848765205591917</v>
+        <v>0.01140537392348051</v>
       </c>
       <c r="C15" t="n">
         <v>14</v>
@@ -618,11 +618,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>province_辽宁</t>
+          <t>cement_price_index</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.008225212804973125</v>
+        <v>0.0111280856654048</v>
       </c>
       <c r="C16" t="n">
         <v>15</v>
@@ -631,11 +631,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>province_陕西</t>
+          <t>province_辽宁</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.008171967230737209</v>
+        <v>0.01098973862826824</v>
       </c>
       <c r="C17" t="n">
         <v>16</v>
@@ -644,11 +644,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>province_湖南</t>
+          <t>total_area</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.007823972962796688</v>
+        <v>0.009988438338041306</v>
       </c>
       <c r="C18" t="n">
         <v>17</v>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.007265040650963783</v>
+        <v>0.008417719975113869</v>
       </c>
       <c r="C19" t="n">
         <v>18</v>
@@ -670,11 +670,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>housing_type_别墅</t>
+          <t>province_湖北</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.007142811547964811</v>
+        <v>0.00830795057117939</v>
       </c>
       <c r="C20" t="n">
         <v>19</v>
@@ -683,11 +683,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>under_floors</t>
+          <t>seismic_intensity</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.004845602437853813</v>
+        <v>0.005738659296184778</v>
       </c>
       <c r="C21" t="n">
         <v>20</v>
@@ -696,11 +696,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>province_山东</t>
+          <t>housing_type_普通住宅</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.003951463848352432</v>
+        <v>0.005034844856709242</v>
       </c>
       <c r="C22" t="n">
         <v>21</v>
@@ -709,11 +709,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>province_湖北</t>
+          <t>province_山东</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.003850492648780346</v>
+        <v>0.004337340593338013</v>
       </c>
       <c r="C23" t="n">
         <v>22</v>
@@ -722,11 +722,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>structure_type_框剪</t>
+          <t>province_福建</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.003472662065178156</v>
+        <v>0.003918804228305817</v>
       </c>
       <c r="C24" t="n">
         <v>23</v>
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.003417818574234843</v>
+        <v>0.003624326782301068</v>
       </c>
       <c r="C25" t="n">
         <v>24</v>
@@ -748,11 +748,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>province_福建</t>
+          <t>foundation_type_桩基础</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.002275910461321473</v>
+        <v>0.003283196361735463</v>
       </c>
       <c r="C26" t="n">
         <v>25</v>
@@ -761,11 +761,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>seismic_intensity</t>
+          <t>foundation_type_筏板基础</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.002261023502796888</v>
+        <v>0.0031644266564399</v>
       </c>
       <c r="C27" t="n">
         <v>26</v>
@@ -774,11 +774,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>structure_type_砌体</t>
+          <t>foundation_type_独立基础</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.001799280988052487</v>
+        <v>0.001582019380293787</v>
       </c>
       <c r="C28" t="n">
         <v>27</v>
@@ -787,11 +787,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>is_prefab</t>
+          <t>province_重庆</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.001785514294169843</v>
+        <v>0.001291302149184048</v>
       </c>
       <c r="C29" t="n">
         <v>28</v>
@@ -800,11 +800,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>foundation_type_筏板基础</t>
+          <t>structure_type_框剪</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.001645429874770343</v>
+        <v>0.001164618995971978</v>
       </c>
       <c r="C30" t="n">
         <v>29</v>
@@ -813,11 +813,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>province_重庆</t>
+          <t>is_prefab</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.001226650085300207</v>
+        <v>0.0008641267195343971</v>
       </c>
       <c r="C31" t="n">
         <v>30</v>
@@ -826,11 +826,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>foundation_type_桩基础</t>
+          <t>housing_type_高档住宅</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0009016724652610719</v>
+        <v>0.0008150180801749229</v>
       </c>
       <c r="C32" t="n">
         <v>31</v>
@@ -839,11 +839,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>foundation_type_独立基础</t>
+          <t>structure_type_框架</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.0007537715719081461</v>
+        <v>0.0007854235009290278</v>
       </c>
       <c r="C33" t="n">
         <v>32</v>
@@ -852,11 +852,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>structure_type_框架</t>
+          <t>housing_type_别墅</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.0006964567000977695</v>
+        <v>0.0005759812192991376</v>
       </c>
       <c r="C34" t="n">
         <v>33</v>
@@ -865,11 +865,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>housing_type_高档住宅</t>
+          <t>under_floors</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.0006705237901769578</v>
+        <v>0.0005405392148531973</v>
       </c>
       <c r="C35" t="n">
         <v>34</v>
@@ -878,11 +878,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>housing_type_普通住宅</t>
+          <t>structure_type_砌体</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.0005740076303482056</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
         <v>35</v>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.0004476197645999491</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
         <v>36</v>
